--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0002T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.38929089425283</v>
+        <v>5.913259770316086</v>
       </c>
       <c r="D2" t="n">
-        <v>23.40207112556544</v>
+        <v>3.802836557904385</v>
       </c>
       <c r="E2" t="n">
-        <v>14.55361999100344</v>
+        <v>2.364963248538059</v>
       </c>
       <c r="F2" t="n">
-        <v>11.89372872946719</v>
+        <v>1.932730918538418</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>49.87241499845159</v>
+        <v>8.104267437248383</v>
       </c>
       <c r="D3" t="n">
-        <v>56.94762385824403</v>
+        <v>9.253988876964655</v>
       </c>
       <c r="E3" t="n">
-        <v>14.55361999100344</v>
+        <v>2.364963248538059</v>
       </c>
       <c r="F3" t="n">
-        <v>11.89372872946719</v>
+        <v>1.932730918538418</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>71.50302802706383</v>
+        <v>11.61924205439787</v>
       </c>
       <c r="D4" t="n">
-        <v>6.574595701788461</v>
+        <v>1.068371801540625</v>
       </c>
       <c r="E4" t="n">
-        <v>14.55361999100344</v>
+        <v>2.364963248538059</v>
       </c>
       <c r="F4" t="n">
-        <v>11.89372872946719</v>
+        <v>1.932730918538418</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>61.9647092078025</v>
+        <v>10.06926524626791</v>
       </c>
       <c r="D5" t="n">
-        <v>21.41333379456667</v>
+        <v>3.479666741617084</v>
       </c>
       <c r="E5" t="n">
-        <v>14.55361999100344</v>
+        <v>2.364963248538059</v>
       </c>
       <c r="F5" t="n">
-        <v>11.89372872946719</v>
+        <v>1.932730918538418</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>51.29689811093399</v>
+        <v>8.335745943026774</v>
       </c>
       <c r="D6" t="n">
-        <v>33.45987779530358</v>
+        <v>5.437230141736833</v>
       </c>
       <c r="E6" t="n">
-        <v>14.55361999100344</v>
+        <v>2.364963248538059</v>
       </c>
       <c r="F6" t="n">
-        <v>11.89372872946719</v>
+        <v>1.932730918538418</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.378654311984</v>
+        <v>7.0490313256974</v>
       </c>
       <c r="D7" t="n">
-        <v>45.14815442057409</v>
+        <v>7.33657509334329</v>
       </c>
       <c r="E7" t="n">
-        <v>14.55361999100344</v>
+        <v>2.364963248538059</v>
       </c>
       <c r="F7" t="n">
-        <v>11.89372872946719</v>
+        <v>1.932730918538418</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>44.49532417814041</v>
+        <v>7.230490178947818</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21613992897183</v>
+        <v>6.210122738457923</v>
       </c>
       <c r="E8" t="n">
-        <v>14.55361999100344</v>
+        <v>2.364963248538059</v>
       </c>
       <c r="F8" t="n">
-        <v>11.89372872946719</v>
+        <v>1.932730918538418</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>60.07313028168722</v>
+        <v>9.761883670774173</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50282958092714</v>
+        <v>5.119209806900661</v>
       </c>
       <c r="E9" t="n">
-        <v>14.55361999100344</v>
+        <v>2.364963248538059</v>
       </c>
       <c r="F9" t="n">
-        <v>11.89372872946719</v>
+        <v>1.932730918538418</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.35703480821005</v>
+        <v>5.583018156334134</v>
       </c>
       <c r="D10" t="n">
-        <v>30.06400589191006</v>
+        <v>4.885400957435384</v>
       </c>
       <c r="E10" t="n">
-        <v>14.55361999100344</v>
+        <v>2.364963248538059</v>
       </c>
       <c r="F10" t="n">
-        <v>11.89372872946719</v>
+        <v>1.932730918538418</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.9392072121306</v>
+        <v>5.352621171971223</v>
       </c>
       <c r="D11" t="n">
-        <v>37.32276956908202</v>
+        <v>6.064950054975829</v>
       </c>
       <c r="E11" t="n">
-        <v>14.55361999100344</v>
+        <v>2.364963248538059</v>
       </c>
       <c r="F11" t="n">
-        <v>11.89372872946719</v>
+        <v>1.932730918538418</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>25.46283473222885</v>
+        <v>4.137710643987189</v>
       </c>
       <c r="D12" t="n">
-        <v>24.50191314646234</v>
+        <v>3.98156088630013</v>
       </c>
       <c r="E12" t="n">
-        <v>14.55361999100344</v>
+        <v>2.364963248538059</v>
       </c>
       <c r="F12" t="n">
-        <v>11.89372872946719</v>
+        <v>1.932730918538418</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>21.50811323796071</v>
+        <v>3.495068401168616</v>
       </c>
       <c r="D13" t="n">
-        <v>22.5408437785222</v>
+        <v>3.662887114009858</v>
       </c>
       <c r="E13" t="n">
-        <v>14.55361999100344</v>
+        <v>2.364963248538059</v>
       </c>
       <c r="F13" t="n">
-        <v>11.89372872946719</v>
+        <v>1.932730918538418</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>29.45543787301181</v>
+        <v>4.786508654364419</v>
       </c>
       <c r="D14" t="n">
-        <v>28.29889648992679</v>
+        <v>4.598570679613103</v>
       </c>
       <c r="E14" t="n">
-        <v>14.55361999100344</v>
+        <v>2.364963248538059</v>
       </c>
       <c r="F14" t="n">
-        <v>11.89372872946719</v>
+        <v>1.932730918538418</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
